--- a/child-0.xlsx
+++ b/child-0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gwd.grpinf.net\AWSCloudDesktop\test-homedrives\AAJO.GWD\Desktop\DL-GOCO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gwd.grpinf.net\AWSCloudDesktop\test-homedrives\AAJO.GWD\Desktop\DL CTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A7A863-F1C0-4186-A5CB-92589763396A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B7A0736-52FC-442B-9156-C90F30C89DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32DF3ACF-5AD2-4B33-978D-05ED67A4544F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13530" xr2:uid="{A2095AD5-0FBC-4AE5-8186-10B99F05B97C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,17 +97,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>386960</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>315985</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171899</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B441E278-69CA-048D-7C87-F3D3F05FA5CB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83F8006B-2EF5-9D35-D1DD-CF8FFD0B37EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -124,7 +124,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="19894160" cy="2066925"/>
+          <a:ext cx="11898385" cy="3219899"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -137,21 +137,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>258572</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>399</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>335123</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>124268</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00D1DF4E-BF6F-1176-D64B-11B59472DA32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{323081D7-53DC-0E9B-1828-B9BCE7929147}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -167,8 +167,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="2476500"/>
-          <a:ext cx="10012172" cy="2857899"/>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="12527123" cy="3172268"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>534836</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>171846</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8334633C-F903-4BAF-EF16-B8C38BACB003}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7429500"/>
+          <a:ext cx="10288436" cy="2838846"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -496,7 +540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1213A297-BC2B-40E5-BA0B-1FDA54D6B175}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86B17A1-9DBB-46D0-9119-11DF6157EF03}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
